--- a/output/full_scan/batch_seq8_2026-10-01.xlsx
+++ b/output/full_scan/batch_seq8_2026-10-01.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7810</v>
+        <v>7730</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>871.2533669616054</v>
+        <v>1158.794449213871</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>235</v>
+        <v>194.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.40368804649817</v>
+        <v>67.16556131698519</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>32.64902997850191</v>
+        <v>21.98484656967</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.872556065725653</v>
+        <v>3.825409393278601</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.8400642635861697</v>
+        <v>1.390158135459099</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6953</v>
+        <v>6933</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>847.5805775584514</v>
+        <v>1114.367765956412</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>252.5</v>
+        <v>394.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>63.59244060835733</v>
+        <v>69.91921845970488</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>16.40843806823013</v>
+        <v>44.35873161655772</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.902632446432776</v>
+        <v>1.71043377898868</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.159186353424241</v>
+        <v>2.332845400448178</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6933</v>
+        <v>6953</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>839.3677659564117</v>
+        <v>1017.580577558451</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>394.5</v>
+        <v>252.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>69.91921853893732</v>
+        <v>63.59244054449265</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>44.35873142949947</v>
+        <v>16.40843813822247</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.71043377898868</v>
+        <v>1.902632446432776</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2.332845402117236</v>
+        <v>1.159186354648235</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7730</v>
+        <v>6944</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>838.794449213871</v>
+        <v>1014.673822326577</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>194.5</v>
+        <v>800</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>67.16556124092189</v>
+        <v>68.67296932619971</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>21.98484650467277</v>
+        <v>22.52312716295131</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3.825409393278601</v>
+        <v>1.75507406266806</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.390158137128171</v>
+        <v>14.46059225396462</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7712</v>
+        <v>7810</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>807.9505530941548</v>
+        <v>1011.253366961606</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>169</v>
+        <v>235</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>63.84958150756059</v>
+        <v>63.40368806104195</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>23.82621861577901</v>
+        <v>32.64902989147251</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.573619681377106</v>
+        <v>1.872556065725653</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.234001073414465</v>
+        <v>0.8400642657003585</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6983</v>
+        <v>7712</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>777.9264557816223</v>
+        <v>977.9505530941548</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>353</v>
+        <v>169</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>58.81761085248501</v>
+        <v>63.84958150756059</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>24.75700286274456</v>
+        <v>23.82621864946185</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.187692574333693</v>
+        <v>1.573619681377106</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-1.169940881064614</v>
+        <v>1.234001073303197</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6907</v>
+        <v>7822</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>768.7874811259195</v>
+        <v>970.511825940125</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>198.5</v>
+        <v>1000</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>58.68589004090192</v>
+        <v>67.42864995057498</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>14.79055331684812</v>
+        <v>15.89185026895742</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.80191293682713</v>
+        <v>1.651182594012503</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.8424402057432744</v>
+        <v>18.59660322999326</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7799</v>
+        <v>6907</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>717.9659093811325</v>
+        <v>908.7874811259196</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>555</v>
+        <v>198.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>71.85420316366751</v>
+        <v>58.68589004090192</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>43.74852537752355</v>
+        <v>14.79055331684812</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.896590938113254</v>
+        <v>1.80191293682713</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>8.536480974672898</v>
+        <v>0.8424402057432744</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6902</v>
+        <v>8021</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>692.363060943353</v>
+        <v>898.6881979744999</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>155</v>
+        <v>503</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>60.48443455967359</v>
+        <v>65.61581446334002</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>32.70019641171413</v>
+        <v>13.6993550978054</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.8486275940627711</v>
+        <v>0.25254764919652</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>2.692565618591764</v>
+        <v>4.780625988041052</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6937</v>
+        <v>6983</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>684.5827349533031</v>
+        <v>892.9264557816223</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>301.5</v>
+        <v>353</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>57.20248404957739</v>
+        <v>58.81761076997135</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>28.495841092631</v>
+        <v>24.75700286274456</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.8273040955021659</v>
+        <v>2.187692574333693</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.7975572596985687</v>
+        <v>-1.169940880396984</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6877</v>
+        <v>7799</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>683.4649022206112</v>
+        <v>887.9659093811325</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>138.5</v>
+        <v>555</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>68.21035103855928</v>
+        <v>71.85420309758015</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>21.83219558232087</v>
+        <v>43.74852540383093</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.446490222061122</v>
+        <v>1.896590938113253</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>2.363311757647905</v>
+        <v>8.53648097511801</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>7751</v>
+        <v>6877</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>675.6171130026365</v>
+        <v>883.4649022206112</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1630</v>
+        <v>138.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>57.71706546624305</v>
+        <v>68.21035100870185</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>14.44154288019909</v>
+        <v>21.83219565868683</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4756694995395664</v>
+        <v>2.446490222061122</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>14.60159946860002</v>
+        <v>2.363311758671589</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6957</v>
+        <v>6962</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>667.5265381850629</v>
+        <v>881.5023671456887</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>384</v>
+        <v>33.15</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>89.5931009765084</v>
+        <v>63.85112070164081</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46.53769197030203</v>
+        <v>12.95273168713862</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>4.852653818506296</v>
+        <v>2.080765298002758</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>13.17388246498843</v>
+        <v>0.2599898546262555</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6840</v>
+        <v>7751</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>658.3537219034026</v>
+        <v>875.6171130026365</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>99.3</v>
+        <v>1630</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,49 +1241,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>58.93195657155436</v>
+        <v>57.71706547879572</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>36.52746668607329</v>
+        <v>14.44154288019909</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6665717209131836</v>
+        <v>0.4756694995395664</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.7066784322678572</v>
+        <v>14.60159946915633</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6944</v>
+        <v>6957</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>649.6738223265768</v>
+        <v>867.5265381850629</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>800</v>
+        <v>384</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>68.67296922725356</v>
+        <v>89.5931009765084</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>22.52312716383711</v>
+        <v>46.53769191139948</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.75507406266806</v>
+        <v>4.852653818506296</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>14.46059225552248</v>
+        <v>13.17388246587855</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>7744</v>
+        <v>7711</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>646.8957680511131</v>
+        <v>840.892074319275</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>537</v>
+        <v>616</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>57.52560500256137</v>
+        <v>62.96978417296471</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>28.62055108693045</v>
+        <v>27.18977551099147</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5208015416627327</v>
+        <v>1.273610605175377</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,11 +1365,11 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.0311829166885786</v>
+        <v>-1.837360730050801</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>633.9462547560514</v>
+        <v>803.9462547560514</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>292</v>
@@ -1403,7 +1403,7 @@
         <v>67.36761061124324</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>34.39449996356012</v>
+        <v>34.3945000398618</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>2.194625475605142</v>
@@ -1412,37 +1412,37 @@
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>9.603712902995738</v>
+        <v>9.603712902795428</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6962</v>
+        <v>6937</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>631.5023671456887</v>
+        <v>794.5827349533031</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>33.15</v>
+        <v>301.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>63.85112068173078</v>
+        <v>57.20248399657535</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>12.95273166422929</v>
+        <v>28.49584105701537</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.080765298002758</v>
+        <v>0.8273040955021659</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,11 +1471,11 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.2599898545928786</v>
+        <v>0.7975572589196451</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>624.3012586772779</v>
+        <v>764.3012586772778</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>314.5</v>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>55.28079596846263</v>
+        <v>55.28079603436567</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>36.09896321962703</v>
+        <v>36.09896320533649</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>0.4169035881985749</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.1142227149480152</v>
+        <v>0.1142227148367318</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>7556</v>
+        <v>6922</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>613.6072124485789</v>
+        <v>755.1086048886608</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>262.5</v>
+        <v>221</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>58.58853327867934</v>
+        <v>64.44193342124356</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>27.08742647318329</v>
+        <v>24.91487379677316</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.8535954396873308</v>
+        <v>0.4907000281135789</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>1.227400964245012</v>
+        <v>3.251014175954182</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7856</v>
+        <v>6906</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>漢測</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>601.7905955986379</v>
+        <v>754.2218051737112</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>4300</v>
+        <v>84</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>43.59771494528519</v>
+        <v>57.64310070837809</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15.21194975707682</v>
+        <v>42.54532701048563</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.344339708299253</v>
+        <v>0.3622703288409562</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-102.3267997365302</v>
+        <v>-0.0975614269112679</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6924</v>
+        <v>6903</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>600.3941617930834</v>
+        <v>736.5068293614593</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>134</v>
+        <v>316</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>57.7352986831124</v>
+        <v>54.41371966836792</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>32.811070531735</v>
+        <v>12.66049345238556</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.4347433737839045</v>
+        <v>1.775167609681573</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.3109165137902856</v>
+        <v>2.579357132140416</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6903</v>
+        <v>7556</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>596.5068293614596</v>
+        <v>728.6072124485789</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>316</v>
+        <v>262.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>54.41371957536195</v>
+        <v>58.5885333251906</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>12.66049346766709</v>
+        <v>27.08742651410658</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.775167609681573</v>
+        <v>0.8535954396873308</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>2.579357131917846</v>
+        <v>1.227400963466106</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6894</v>
+        <v>7714</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>585.2720270564241</v>
+        <v>709.0096514826917</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>360</v>
+        <v>169.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>53.57327987089258</v>
+        <v>50.83707296688991</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>29.73279446539445</v>
+        <v>21.35132514184773</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4712311092374711</v>
+        <v>0.8441841392393529</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.2590028613112949</v>
+        <v>-0.6913994910306158</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6922</v>
+        <v>6885</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>585.1086048886608</v>
+        <v>703.221972581246</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>221</v>
+        <v>31.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>64.44193342524622</v>
+        <v>70.21509370224774</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>24.91487377609383</v>
+        <v>61.24325107663346</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4907000281135789</v>
+        <v>0.5974665236836737</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>3.251014175397827</v>
+        <v>0.20368081682967</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>7822</v>
+        <v>7795</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>580.511825940125</v>
+        <v>692.0718620650764</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1000</v>
+        <v>536</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>67.42864991804122</v>
+        <v>56.95764215865968</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>15.89185024969316</v>
+        <v>16.18672579881066</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.651182594012503</v>
+        <v>1.494185871671521</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,11 +1895,11 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>18.59660322153665</v>
+        <v>0.8686250029232783</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>575.3975723445209</v>
+        <v>690.3975723445209</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>205</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>62.48352429535915</v>
+        <v>62.48352425951291</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>30.47420126884162</v>
+        <v>30.47420129958721</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.9765433633754262</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.0507497785548514</v>
+        <v>-0.0507497788886812</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>7714</v>
+        <v>7827</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>569.0096514826918</v>
+        <v>680.4333571230345</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>169.5</v>
+        <v>165</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>50.83707284462471</v>
+        <v>64.33884413988281</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>21.35132508871187</v>
+        <v>16.55432901538448</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8441841392393529</v>
+        <v>1.749607739613465</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.691399490362989</v>
+        <v>1.339636140169627</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7711</v>
+        <v>6902</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>565.892074319275</v>
+        <v>672.363060943353</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>616</v>
+        <v>155</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>62.96978418162794</v>
+        <v>60.48443456520947</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>27.18977545201678</v>
+        <v>32.70019648468691</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.273610605175377</v>
+        <v>0.8486275940627711</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-1.837360729383224</v>
+        <v>2.692565618614038</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6885</v>
+        <v>8028</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>553.221972581246</v>
+        <v>667.8728739060672</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>31.5</v>
+        <v>280</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>70.21509369200817</v>
+        <v>61.84346978055083</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>61.24325107663347</v>
+        <v>23.20602804586892</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5974665236836737</v>
+        <v>0.7872873906067174</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.2036808169298165</v>
+        <v>6.236386070837062</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7795</v>
+        <v>6840</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>552.0718620650764</v>
+        <v>658.3537219034026</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>536</v>
+        <v>99.3</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>56.95764216047397</v>
+        <v>58.9319565484021</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>16.18672578363295</v>
+        <v>36.52746679465976</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.494185871671521</v>
+        <v>0.6665717209131836</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.8686250030345413</v>
+        <v>-0.7066784318450265</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7717</v>
+        <v>7744</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>545.564827185378</v>
+        <v>646.895768051113</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>55.3038579711708</v>
+        <v>57.52560485763755</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>18.66102381251078</v>
+        <v>28.62055092089359</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.9639481711748944</v>
+        <v>0.5208015416627327</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>2.425724213353341</v>
+        <v>-0.0311829105686456</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7827</v>
+        <v>6859</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>545.4333571230345</v>
+        <v>641.9891370004121</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>165</v>
+        <v>120.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>64.33884402535259</v>
+        <v>58.5607901357609</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>16.55432900432106</v>
+        <v>39.58369763450583</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.749607739613465</v>
+        <v>0.5157541157880724</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1.339636139546481</v>
+        <v>-0.0889728309282071</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6906</v>
+        <v>8016</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>529.2218051737113</v>
+        <v>640.4111814156072</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>84</v>
+        <v>288.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,49 +2301,49 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>57.64310084994538</v>
+        <v>52.81240637856985</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>42.54532697013624</v>
+        <v>9.717975282756733</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3622703288409562</v>
+        <v>1.014460084218608</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.0975614269112679</v>
+        <v>1.347645494665298</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6859</v>
+        <v>7631</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>526.9891370004125</v>
+        <v>634.9554899062505</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>120.5</v>
+        <v>145.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>58.56079004073459</v>
+        <v>58.48018773680796</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>39.58369755934011</v>
+        <v>18.2105757093906</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5157541157880724</v>
+        <v>4.26046525961394</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.0889728307056612</v>
+        <v>0.4993433983330867</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8028</v>
+        <v>8033</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>497.8728739060672</v>
+        <v>633.73209443857</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>280</v>
+        <v>175.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>61.84346963398807</v>
+        <v>50.42651255450522</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>23.20602763085243</v>
+        <v>7.073580675858199</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.7872873906067174</v>
+        <v>0.6643221429816979</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>6.236386074286479</v>
+        <v>0.753952848108391</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7631</v>
+        <v>7734</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>494.9554899062505</v>
+        <v>633.0588432144596</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>145.5</v>
+        <v>2795</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>58.48018778580757</v>
+        <v>51.28479654832488</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18.21057572927818</v>
+        <v>15.69954736761725</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>4.26046525961394</v>
+        <v>1.528926567464501</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.4993433981105422</v>
+        <v>28.90224860785145</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6862</v>
+        <v>6838</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>494.6047090525325</v>
+        <v>618.5308898654124</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>142</v>
+        <v>25.8</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>55.13214357397051</v>
+        <v>65.49023397145341</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15.29145201344759</v>
+        <v>34.6764859162561</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2.47017761721984</v>
+        <v>0.7299509097484095</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1.17884137967476</v>
+        <v>0.2202180247380323</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7765</v>
+        <v>6925</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>493.7059596204766</v>
+        <v>618.0674289595953</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>236.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>55.35998731929462</v>
+        <v>71.83139729523218</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>38.02005896646387</v>
+        <v>33.22725569701605</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.2542313253773264</v>
+        <v>2.274904220884668</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.4421574435626398</v>
+        <v>2.143407275744523</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8034</v>
+        <v>6967</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>479.0101255315433</v>
+        <v>617.2636683232253</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>19.95</v>
+        <v>71.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>48.94955216565925</v>
+        <v>61.41241923261427</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>20.71569191590902</v>
+        <v>13.87055995057998</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5819191726042908</v>
+        <v>1.434019772156925</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>5</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.0020842191317633</v>
+        <v>0.660561575094754</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6869</v>
+        <v>6909</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>470.7110329199354</v>
+        <v>613.561598708553</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>69.40000000000001</v>
+        <v>42.75</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,49 +2672,49 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55.34898772628666</v>
+        <v>55.39421444702938</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>23.58982503297698</v>
+        <v>20.53300802129455</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.171103291993541</v>
+        <v>0.453205197586916</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.6280025538670667</v>
+        <v>0.2068908030968124</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6910</v>
+        <v>6862</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>463.7233649964329</v>
+        <v>609.6047090525324</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>26.8</v>
+        <v>142</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>66.99450174385169</v>
+        <v>55.13214327885049</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>34.0681973044518</v>
+        <v>15.29145203974296</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.285659241077162</v>
+        <v>2.47017761721984</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.2050460534805362</v>
+        <v>1.178841380453651</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7734</v>
+        <v>6910</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>463.0588432144596</v>
+        <v>603.7233649964329</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2795</v>
+        <v>26.8</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.2847965721274</v>
+        <v>66.99450170648635</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>15.69954734708819</v>
+        <v>34.06819716931367</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.528926567464501</v>
+        <v>1.285659241077162</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>28.90224860228791</v>
+        <v>0.2050460534805362</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>7770</v>
+        <v>7856</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>漢測</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>455.6925482892038</v>
+        <v>601.7905955986379</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>41.45</v>
+        <v>4300</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,49 +2831,49 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>58.67948945545786</v>
+        <v>43.59771494528519</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>8.813866411005263</v>
+        <v>15.21194975707682</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6157559635965074</v>
+        <v>1.344339708299253</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M45" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.4875980613057145</v>
+        <v>-102.3267997365302</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6838</v>
+        <v>6924</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>448.5308898654124</v>
+        <v>600.3941617930834</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>25.8</v>
+        <v>134</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>65.49023406223958</v>
+        <v>57.735298748596</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>34.67648587022268</v>
+        <v>32.81107056036823</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.7299509097484095</v>
+        <v>0.4347433737839045</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.2202180247380323</v>
+        <v>-0.3109165144356485</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6967</v>
+        <v>7770</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>447.2636683232253</v>
+        <v>595.6925482892038</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>71.5</v>
+        <v>41.45</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>61.41241930115373</v>
+        <v>58.67948948087176</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>13.87055996314546</v>
+        <v>8.813866423826243</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.434019772156925</v>
+        <v>0.6157559635965074</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.6605615748722244</v>
+        <v>0.4875980613057145</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7749</v>
+        <v>6894</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>438.6350686092101</v>
+        <v>585.2720270564239</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>401.5</v>
+        <v>360</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>64.11089201652374</v>
+        <v>53.57327987089258</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>20.84340343223192</v>
+        <v>29.73279451415312</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.115552048965323</v>
+        <v>0.4712311092374711</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>4.459127149833779</v>
+        <v>-0.2590028624239897</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7768</v>
+        <v>6869</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>426.7212083616383</v>
+        <v>580.7110329199354</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>301</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>58.8034535059404</v>
+        <v>55.34898764467438</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>23.5192561288872</v>
+        <v>23.58982500622756</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.455322081103361</v>
+        <v>1.171103291993541</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>3.829282561697085</v>
+        <v>0.6280025535332542</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>7828</v>
+        <v>7749</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>424.5965751345426</v>
+        <v>578.63506860921</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>1875</v>
+        <v>401.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>49.26662015696101</v>
+        <v>64.11089195086495</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>22.59207497069391</v>
+        <v>20.84340369817496</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4203395539276053</v>
+        <v>1.115552048965323</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-19.82023648370301</v>
+        <v>4.459127161628537</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6919</v>
+        <v>7728</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>421.844944031282</v>
+        <v>569.5809030476374</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>79.09999999999999</v>
+        <v>649</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>34.788452680235</v>
+        <v>57.4890309450453</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>29.60582388916076</v>
+        <v>17.66375560065575</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.439977545315248</v>
+        <v>2.1431449755513</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.3546240461942416</v>
+        <v>3.383206246112023</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, stronger_than_market, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6925</v>
+        <v>7717</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>418.0674289595953</v>
+        <v>545.564827185378</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>551</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>71.83139741841825</v>
+        <v>55.3038579711708</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>33.22725569701605</v>
+        <v>18.66102381251078</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2.274904220884668</v>
+        <v>0.9639481711748944</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>2.143407275855801</v>
+        <v>2.425724213353341</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8016</v>
+        <v>7768</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>410.4111814156072</v>
+        <v>541.7212083616382</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>288.5</v>
+        <v>301</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.81240633211747</v>
+        <v>58.80345347007821</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>9.717975235839036</v>
+        <v>23.51925621526696</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.014460084218608</v>
+        <v>1.455322081103361</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>1.347645494887813</v>
+        <v>3.829282562030913</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8033</v>
+        <v>7825</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>和亞智慧</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>398.73209443857</v>
+        <v>524.3614500659896</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>175.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>50.42651235218958</v>
+        <v>50.76122099003995</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>7.07358051812413</v>
+        <v>20.97407295609021</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.6643221429816979</v>
+        <v>0.7306979306755302</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.7539528489985932</v>
+        <v>-0.7796582559757032</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6955</v>
+        <v>7765</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>395.730413095824</v>
+        <v>513.7059596204765</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>95.2</v>
+        <v>236.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>49.40663410636693</v>
+        <v>55.35998742112968</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>6.371263017731343</v>
+        <v>38.02005903413711</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.000418698253623</v>
+        <v>0.2542313253773264</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>1.491405092786104</v>
+        <v>0.4421574435626398</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>7747</v>
+        <v>7547</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>392.3991947215474</v>
+        <v>490.6308490100421</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>111.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>51.5777236443016</v>
+        <v>76.99640659785538</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>6.821444785234726</v>
+        <v>23.4136773858944</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>16.46336364158106</v>
+        <v>2.46308490100421</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>1.741657124203917</v>
+        <v>1.826474293501639</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>7842</v>
+        <v>8034</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>380.3338665979114</v>
+        <v>479.0101255315369</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>97.7</v>
+        <v>19.95</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>50.3732129110044</v>
+        <v>48.94955253758071</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>16.02961503373736</v>
+        <v>20.71569194326595</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.2047197813501043</v>
+        <v>0.5819191726042908</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.3233354537090406</v>
+        <v>-0.0020842191762694</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6887</v>
+        <v>6934</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>378.5772720850927</v>
+        <v>474.3775992873205</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>37.95</v>
+        <v>75.2</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>50.59619044971479</v>
+        <v>51.80925799883573</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>38.71396521679403</v>
+        <v>19.30764483395595</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.5930230553016848</v>
+        <v>0.9106617074064556</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0390187351410155</v>
+        <v>0.0660336940457768</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6909</v>
+        <v>6994</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>378.5615987085533</v>
+        <v>426.7187482483974</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>42.75</v>
+        <v>29.15</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>55.39421462716624</v>
+        <v>42.39004854191169</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>20.53300797923503</v>
+        <v>46.40112681149046</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.453205197586916</v>
+        <v>1.351753434773104</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.2068908030077898</v>
+        <v>0.1487156564291774</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7728</v>
+        <v>6947</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>369.5809030476372</v>
+        <v>425.1012706974721</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>649</v>
+        <v>68.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>57.48903092944865</v>
+        <v>45.55678219234582</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>17.66375558803014</v>
+        <v>9.323462212945948</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2.1431449755513</v>
+        <v>1.411249170608761</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>3.383206246223408</v>
+        <v>0.3508852377517559</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, cci_momentum, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>7839</v>
+        <v>7828</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>366.7236601756368</v>
+        <v>424.5965751345427</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>43</v>
+        <v>1875</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>42.14778450771468</v>
+        <v>49.2666201545668</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>33.50728469464296</v>
+        <v>22.59207497115612</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2.061410397361394</v>
+        <v>0.4203395539276053</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0430231621276144</v>
+        <v>-19.8202364832578</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>7704</v>
+        <v>6916</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>363.0073620397431</v>
+        <v>424.2422737493837</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>61.2</v>
+        <v>18.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>48.72956005540136</v>
+        <v>50.65579991109136</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>18.7119971546511</v>
+        <v>17.79380462506613</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7320044874638002</v>
+        <v>0.4588788699366293</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0396011607969297</v>
+        <v>0.0464255367024961</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>7610</v>
+        <v>6919</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>359.4250663155402</v>
+        <v>421.8449440312821</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>1780</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.26410267320956</v>
+        <v>34.7884526118647</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>11.42703029023974</v>
+        <v>29.60582393076519</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5746698486833055</v>
+        <v>0.439977545315248</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-13.09312413340882</v>
+        <v>0.3546240465280545</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6958</v>
+        <v>8011</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>353.5417294555842</v>
+        <v>417.337842268507</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>17.5</v>
+        <v>16.05</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,49 +3838,49 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>50.44473724844952</v>
+        <v>52.63894611501856</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>25.25474622144807</v>
+        <v>22.52148295315</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.3213093739985462</v>
+        <v>0.3659222595413471</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0126371344598157</v>
+        <v>0.0629618301384695</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6952</v>
+        <v>7689</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>352.6281050448924</v>
+        <v>395.9251679039047</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>38.8</v>
+        <v>161</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>52.04180885983011</v>
+        <v>41.62652849011026</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>11.74786590420763</v>
+        <v>23.81416680010622</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4215076100887076</v>
+        <v>1.367469927951127</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.2383769678665613</v>
+        <v>1.066027429623102</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6914</v>
+        <v>6955</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>343.2011742251611</v>
+        <v>395.730413095824</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>118</v>
+        <v>95.2</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>22.07298276232514</v>
+        <v>49.40663406115491</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>43.03158428412947</v>
+        <v>6.371263017731343</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.684469788236554</v>
+        <v>1.000418698253623</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.6690605977010398</v>
+        <v>1.491405092229739</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6997</v>
+        <v>7747</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>337.2194868513884</v>
+        <v>392.3991947215474</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0</v>
+        <v>111.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>37.21331957121449</v>
+        <v>51.57772362961964</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>9.664700241217831</v>
+        <v>6.821444842475176</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.0019598236158745</v>
+        <v>16.46336364158106</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-2.299402326846991</v>
+        <v>1.741657124537731</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6923</v>
+        <v>6895</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>329.0226710684921</v>
+        <v>390.2797331553353</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>42.92476173142735</v>
+        <v>58.40215668539328</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>16.08555182008539</v>
+        <v>16.41340752724228</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6834732239905822</v>
+        <v>0.843848676963748</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.1269554130015634</v>
+        <v>-0.5817796244337092</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7788</v>
+        <v>7786</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>324.7555516051245</v>
+        <v>388.4811582560525</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>290.5</v>
+        <v>118.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.33928848835095</v>
+        <v>48.66330236547383</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>16.40794364931923</v>
+        <v>13.82458073655476</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.160411545644631</v>
+        <v>0.6818011373877972</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-2.696646202503074</v>
+        <v>0.4814289756494545</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>7825</v>
+        <v>7820</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>和亞智慧</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>324.3614500659897</v>
+        <v>380.5573972014381</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>85.59999999999999</v>
+        <v>110</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>50.76122096758128</v>
+        <v>51.00905098351281</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>20.97407281744174</v>
+        <v>10.75646185827113</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.7306979306755302</v>
+        <v>0.6009121630738875</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>2</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.7796582552306353</v>
+        <v>1.558889312091634</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6949</v>
+        <v>7842</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>321.7103080926757</v>
+        <v>380.3338665979114</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>49.4</v>
+        <v>97.7</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>25.65606809240171</v>
+        <v>50.37321236914841</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>44.55330992295926</v>
+        <v>16.02961515092059</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.2484142982754566</v>
+        <v>0.2047197813501043</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>11.29351461477873</v>
+        <v>-0.3233354521512369</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6947</v>
+        <v>6887</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>315.101270697472</v>
+        <v>378.5772720850927</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>68.5</v>
+        <v>37.95</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45.55678216818043</v>
+        <v>50.59619032298103</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>9.323462176656395</v>
+        <v>38.7139651884781</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.411249170608761</v>
+        <v>0.5930230553016848</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.3508852377740092</v>
+        <v>-0.0390187351855191</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6918</v>
+        <v>6958</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>313.9366148240098</v>
+        <v>373.5417294555842</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>73.90000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.86386845007321</v>
+        <v>50.44473738326824</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>32.3785756894118</v>
+        <v>25.25474622128236</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.7936614824009829</v>
+        <v>0.3213093739985462</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.2015505420234357</v>
+        <v>0.0126371343930511</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6971</v>
+        <v>7839</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>312.2282964256505</v>
+        <v>366.7236601756369</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>23.3</v>
+        <v>43</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>22.82962921489545</v>
+        <v>42.14777394824832</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>28.6652749799096</v>
+        <v>33.5072892186084</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.2438650694600428</v>
+        <v>2.061410397361394</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.106778807279551</v>
+        <v>0.0430231768154338</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6916</v>
+        <v>7704</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>309.2422737493837</v>
+        <v>363.0073620397431</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>18.5</v>
+        <v>61.2</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>50.65579987207125</v>
+        <v>48.72955989634377</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>17.79380463783341</v>
+        <v>18.71199711504982</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4588788699366293</v>
+        <v>0.7320044874638002</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.046425536724747</v>
+        <v>-0.0396011606300274</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8011</v>
+        <v>7610</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>307.3378422685074</v>
+        <v>359.4250663155402</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>16.05</v>
+        <v>1780</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>52.63894600620781</v>
+        <v>49.2641026743335</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>22.52148295224726</v>
+        <v>11.42703029081329</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3659222595413471</v>
+        <v>0.5746698486833055</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.06296183016072571</v>
+        <v>-13.09312413363135</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6988</v>
+        <v>6952</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>307.2542694003023</v>
+        <v>352.6281050448924</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>11.65</v>
+        <v>38.8</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45.95112300005036</v>
+        <v>52.04180886350157</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>10.39943506037309</v>
+        <v>11.74786589665199</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.416812744079908</v>
+        <v>0.4215076100887076</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0123709752425333</v>
+        <v>0.2383769678554279</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6863</v>
+        <v>7721</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>304.2256574526685</v>
+        <v>352.5947958872243</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>95.5</v>
+        <v>61.9</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>37.07092400364214</v>
+        <v>52.1049241814344</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>23.18524338905827</v>
+        <v>15.57635688423324</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5639011720908897</v>
+        <v>0.5271087967985343</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.4983963794996229</v>
+        <v>0.3097099958735614</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6921</v>
+        <v>6914</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>301.0412770163901</v>
+        <v>343.2011742251613</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>66.40000000000001</v>
+        <v>118</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>53.19043354180539</v>
+        <v>22.07298253973161</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>19.42281051243486</v>
+        <v>43.03158430569064</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5665022093586165</v>
+        <v>1.684469788236554</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.5755586667513498</v>
+        <v>0.6690605981461228</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7818</v>
+        <v>6854</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>300.2984867846013</v>
+        <v>339.8576140180423</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>60.1</v>
+        <v>93.7</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>39.43767123103367</v>
+        <v>52.41191097822722</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>16.1371968347578</v>
+        <v>14.3256915739567</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.9769867046693528</v>
+        <v>0.9105504003154732</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.1545161416739942</v>
+        <v>0.5716094959327536</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6908</v>
+        <v>6997</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>297.9347724259334</v>
+        <v>337.2194868513883</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>31.38865577994791</v>
+        <v>37.21331956899915</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>21.55483003649508</v>
+        <v>9.664700272746892</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>4.496697094836325</v>
+        <v>0.0019598236158745</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.2009844428429839</v>
+        <v>-2.299402326735721</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7547</v>
+        <v>6928</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>290.6308490100421</v>
+        <v>330.9112784187351</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>46.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>76.99640727988741</v>
+        <v>46.48470699917159</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>23.4136773858944</v>
+        <v>10.90486082518216</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>2.46308490100421</v>
+        <v>1.186847791701401</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>1.82647429416926</v>
+        <v>-0.008810179551976801</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>7689</v>
+        <v>6923</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>285.9251679039047</v>
+        <v>329.0226710684866</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>41.62652849011026</v>
+        <v>42.92476152530222</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>23.81416680010622</v>
+        <v>16.08555174850418</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.367469927951127</v>
+        <v>0.6834732239905822</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>1.066027429623102</v>
+        <v>-0.1269554127344977</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>7823</v>
+        <v>7788</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>282.7870774077105</v>
+        <v>324.7555516051245</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>79.90000000000001</v>
+        <v>290.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>43.28509713612263</v>
+        <v>51.33928847061378</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13.7503160453428</v>
+        <v>16.40794380669414</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.344574414344153</v>
+        <v>1.160411545644631</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0245310876993601</v>
+        <v>-2.696646202503074</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7750</v>
+        <v>6949</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>282.2478958728392</v>
+        <v>321.7103080926757</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>1895</v>
+        <v>49.4</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>36.79634037226628</v>
+        <v>25.65606806629131</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>19.88822394443026</v>
+        <v>44.5533099483871</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4779535856446262</v>
+        <v>0.2484142982754566</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-8.751421037833452</v>
+        <v>11.29351462603003</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>7786</v>
+        <v>7818</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>278.4811582560527</v>
+        <v>320.2984867846013</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>118.5</v>
+        <v>60.1</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>48.66330274836393</v>
+        <v>39.43767239209447</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>13.82458073624239</v>
+        <v>16.1371968347578</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6818011373877972</v>
+        <v>0.9769867046693528</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.4814289743141946</v>
+        <v>0.1545161415627234</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8024</v>
+        <v>6908</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>275.0492267687605</v>
+        <v>317.9347724259334</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>12.35</v>
+        <v>27.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>32.35158474553126</v>
+        <v>31.38865609648198</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>12.03933255316297</v>
+        <v>21.55483004245178</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.189627654750893</v>
+        <v>4.496697094836325</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0028128195837217</v>
+        <v>-0.2009844432658127</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>7740</v>
+        <v>6918</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>274.2230357168878</v>
+        <v>313.9366148240098</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>102.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>25.64628547949637</v>
+        <v>44.86386841676276</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>25.99676220472391</v>
+        <v>32.37857567412042</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.9309100537791388</v>
+        <v>0.7936614824009829</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-1.727027719408533</v>
+        <v>-0.201550542245975</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7855</v>
+        <v>6971</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>273.9043090733323</v>
+        <v>312.2282964256505</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>41.4</v>
+        <v>23.3</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>16.97477499838526</v>
+        <v>22.82962924005288</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>59.46026569601744</v>
+        <v>28.66527513161446</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.5989878562557812</v>
+        <v>0.2438650694600428</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>1.159793272282898</v>
+        <v>-0.1067788073574393</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>7769</v>
+        <v>6988</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>271.5233294473109</v>
+        <v>307.2542694003023</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>5490</v>
+        <v>11.65</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>37.65793726972338</v>
+        <v>45.95112290718973</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>12.44545374705377</v>
+        <v>10.39943500034446</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4705367901088602</v>
+        <v>1.416812744079908</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-86.69929661393824</v>
+        <v>-0.0123709751535152</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>7805</v>
+        <v>6863</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>270.8786005602213</v>
+        <v>304.2256574526685</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>490</v>
+        <v>95.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>33.0976455008482</v>
+        <v>37.07092387753876</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>33.91944824687403</v>
+        <v>23.18524346313465</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.066053655489642</v>
+        <v>0.5639011720908897</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>3.907023682558307</v>
+        <v>0.498396379054522</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>7821</v>
+        <v>6921</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>263.8364761408281</v>
+        <v>301.0412770163901</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>35.85</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>22.73091780385126</v>
+        <v>53.19043354180539</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>27.40695822022064</v>
+        <v>19.42281051243486</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.283647614082814</v>
+        <v>0.5665022093586165</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.301991122463031</v>
+        <v>0.5755586667513498</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6899</v>
+        <v>6901</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>263.0049544064866</v>
+        <v>293.6321671170766</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>49.5</v>
+        <v>16.65</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>44.55749940510064</v>
+        <v>58.10737285108942</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>23.11662139259363</v>
+        <v>18.37268694628672</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.057510268834985</v>
+        <v>1.902825851051072</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0553535175441152</v>
+        <v>0.2563378229825935</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>volume_break, rsi_strong, market_above_ma60, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6965</v>
+        <v>7821</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>256.4105830859919</v>
+        <v>283.8364761408281</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>63.2</v>
+        <v>35.85</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>19.93966552205862</v>
+        <v>22.73091768601737</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>47.1996450952648</v>
+        <v>27.40695822065772</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.041058308599194</v>
+        <v>1.283647614082814</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.6311487366946698</v>
+        <v>-0.3019911223962646</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5456,21 +5456,21 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6895</v>
+        <v>7823</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>250.279733155335</v>
+        <v>282.7870774077105</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>151</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>58.40215650843265</v>
+        <v>43.28509713612263</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>16.41340746029768</v>
+        <v>13.7503160453428</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.843848676963748</v>
+        <v>1.344574414344153</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.5817796265478572</v>
+        <v>-0.0245310876993601</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, foreign_buy_3d, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6934</v>
+        <v>7750</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>249.3775992873205</v>
+        <v>282.2478958728392</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>75.2</v>
+        <v>1895</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>51.80925798885922</v>
+        <v>36.79634034884455</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>19.30764483345496</v>
+        <v>19.88822396666519</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.9106617074064556</v>
+        <v>0.4779535856446262</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0660336940902734</v>
+        <v>-8.751421030712237</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6913</v>
+        <v>7715</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>248.9382122025117</v>
+        <v>279.5961420308621</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>129</v>
+        <v>28.35</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>43.07254291193512</v>
+        <v>45.3693292954259</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>17.72614133360204</v>
+        <v>28.60677011502663</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.2592684214706267</v>
+        <v>0.7264604372139435</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.2342295049843716</v>
+        <v>0.1726432758070551</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6994</v>
+        <v>8024</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>246.7187482483974</v>
+        <v>275.0492267687605</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>29.15</v>
+        <v>12.35</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>42.39004866465051</v>
+        <v>32.35158482900165</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>46.40112685881623</v>
+        <v>12.03933255316297</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.351753434773104</v>
+        <v>1.189627654750893</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.1487156563401597</v>
+        <v>0.0028128194835771</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>7721</v>
+        <v>7855</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>242.5947958872247</v>
+        <v>273.9043090733323</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>61.9</v>
+        <v>41.4</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>52.10492429980564</v>
+        <v>16.97477499838526</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>15.57635690467123</v>
+        <v>59.46026569601744</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5271087967985343</v>
+        <v>0.5989878562557812</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.3097099961406121</v>
+        <v>1.159793272282898</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>7820</v>
+        <v>7769</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>240.5573972014381</v>
+        <v>271.5233294473168</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>110</v>
+        <v>5490</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>51.00905105072378</v>
+        <v>37.65793726972338</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>10.75646175397526</v>
+        <v>12.44545368823441</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6009121630738875</v>
+        <v>0.4705367901088602</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>1.558889309977476</v>
+        <v>-86.69929660503647</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6855</v>
+        <v>7805</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>238.2742872383508</v>
+        <v>270.8786005602213</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>44.1721327561106</v>
+        <v>33.09764542918602</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>8.909860517345132</v>
+        <v>33.91944829937929</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.0012555243069505</v>
+        <v>1.066053655489642</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-6.246486128277997</v>
+        <v>3.907023684116094</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6865</v>
+        <v>7740</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>231.886673633139</v>
+        <v>264.2230357168875</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>27.65</v>
+        <v>102.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>54.35165798518582</v>
+        <v>25.64628527470438</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.44088480022437</v>
+        <v>25.99676232209718</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6957843864825239</v>
+        <v>0.9309100537791388</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0063976438531923</v>
+        <v>-1.727027716960567</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7760</v>
+        <v>6899</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>230.9657689297785</v>
+        <v>263.0049544064866</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>32.5</v>
+        <v>49.5</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>43.54729279332248</v>
+        <v>44.55749943438322</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>25.0683002340296</v>
+        <v>23.11662143115444</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.150815024425276</v>
+        <v>1.057510268834985</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0025450299852472</v>
+        <v>0.0553535174328472</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6854</v>
+        <v>7780</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>229.8576140180422</v>
+        <v>256.7327645749583</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>93.7</v>
+        <v>16.15</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>52.4119108294415</v>
+        <v>41.65206314068463</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>14.32569155121612</v>
+        <v>17.25847612528268</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.9105504003154732</v>
+        <v>1.269783074891864</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.5716094971567363</v>
+        <v>0.0060179944853694</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6951</v>
+        <v>6965</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>229.1193799856513</v>
+        <v>256.4105830859919</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>69.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>36.32679888274728</v>
+        <v>19.93966543542664</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>29.99000845629828</v>
+        <v>47.19964478572429</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.777260041062492</v>
+        <v>1.041058308599194</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0138169067489204</v>
+        <v>-0.6311487368059443</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6928</v>
+        <v>7760</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>220.9112784187353</v>
+        <v>250.9657689297788</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>46.5</v>
+        <v>32.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>46.48470655713349</v>
+        <v>43.54729220305481</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>10.9048607536863</v>
+        <v>25.06830024715984</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.186847791701401</v>
+        <v>1.150815024425276</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0088101791291425</v>
+        <v>0.002545030341311</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>7736</v>
+        <v>6913</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>206.5220827857114</v>
+        <v>248.9382122025117</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>68.7</v>
+        <v>129</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46.90550607108275</v>
+        <v>43.07254295018436</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.47936727072028</v>
+        <v>17.72614130419269</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>2.814503589024547</v>
+        <v>0.2592684214706267</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0018071131927487</v>
+        <v>-0.2342295050956524</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>7738</v>
+        <v>6855</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>206.4398629837945</v>
+        <v>238.2742872383508</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>34.567521460425</v>
+        <v>44.17213305865583</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18.00486837778346</v>
+        <v>8.909861465947316</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.244786779802095</v>
+        <v>0.0012555243069505</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.7135305638024469</v>
+        <v>-6.246486158321261</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>7402</v>
+        <v>6865</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>204.9460967640128</v>
+        <v>231.886673633139</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>100.5</v>
+        <v>27.65</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>44.19644023225901</v>
+        <v>54.35165799279562</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>14.66300581744241</v>
+        <v>13.44088490267658</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5329577539410449</v>
+        <v>0.6957843864825239</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.2020456127076051</v>
+        <v>0.0063976442537709</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>7791</v>
+        <v>6951</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>198.2298212567368</v>
+        <v>229.1193799856512</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>54.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>36.12319914403828</v>
+        <v>36.32679876022056</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>16.95512732374958</v>
+        <v>29.99000866936802</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.98743257520992</v>
+        <v>0.777260041062492</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,11 +6294,11 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0757998438335242</v>
+        <v>-0.0138169067934355</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6315,7 @@
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>190.0419627787082</v>
+        <v>210.0419627787082</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>64.5</v>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>29.30097906499068</v>
+        <v>29.3009791071168</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.40385171096554</v>
+        <v>17.40385177143718</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>1.904196277870822</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-1.450478853476752</v>
+        <v>-1.450478853543517</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>7722</v>
+        <v>7736</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>189.7754665297055</v>
+        <v>206.5220827857114</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>260</v>
+        <v>68.7</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>38.68886336095226</v>
+        <v>46.90550607108275</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>15.85821370829088</v>
+        <v>15.47936723137882</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.4991976168559056</v>
+        <v>2.814503589024547</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.009066257420382501</v>
+        <v>-0.0018071131927487</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>7732</v>
+        <v>7738</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>178.1796535884263</v>
+        <v>206.439862983796</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>33.2</v>
+        <v>156</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>51.26324007629208</v>
+        <v>34.56752128212277</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>9.676005935045721</v>
+        <v>18.0048684091131</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.051777818476754</v>
+        <v>0.244786779802095</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.5855103864162867</v>
+        <v>-0.7135305632460875</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6969</v>
+        <v>7402</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>168.6465400399911</v>
+        <v>204.9460967640128</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>30.45</v>
+        <v>100.5</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>40.10741830680593</v>
+        <v>44.19644042777563</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>15.43959673882804</v>
+        <v>14.66300588396574</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.92591325165268</v>
+        <v>0.5329577539410449</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.3383529278369732</v>
+        <v>0.2020456121067368</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6873</v>
+        <v>7791</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>166.1648560838925</v>
+        <v>198.2298212567368</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>54.8</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>41.44909136282626</v>
+        <v>36.12319904997047</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>16.92013217112418</v>
+        <v>16.95512725944224</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.8655224415612686</v>
+        <v>1.98743257520992</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.2709081913373543</v>
+        <v>0.0757998439447906</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>7715</v>
+        <v>7722</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>164.5961420308622</v>
+        <v>189.7754665297058</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>28.35</v>
+        <v>260</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>45.36932944340487</v>
+        <v>38.68886343314705</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>28.60677011199666</v>
+        <v>15.85821356650653</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.7264604372139435</v>
+        <v>0.4991976168559056</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.1726432758404344</v>
+        <v>-0.0090662643191592</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>7705</v>
+        <v>7732</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>163.6304006189191</v>
+        <v>178.1796535884262</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>29.7</v>
+        <v>33.2</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>39.91397850012592</v>
+        <v>51.26324007629208</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>11.51569553297905</v>
+        <v>9.676005977319736</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.4277513901819315</v>
+        <v>1.051777818476754</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0059072102756348</v>
+        <v>0.5855103863495241</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>7780</v>
+        <v>6969</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>146.7327645749583</v>
+        <v>168.6465400399911</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>16.15</v>
+        <v>30.45</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>41.65205947955609</v>
+        <v>40.10741833446675</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>17.25847775209265</v>
+        <v>15.43959673882804</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.269783074891864</v>
+        <v>0.92591325165268</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0060179990762808</v>
+        <v>-0.3383529279482374</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6931</v>
+        <v>6873</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>144.3634159972653</v>
+        <v>166.1648560838925</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>38.9</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>37.80061079771254</v>
+        <v>41.44909125699213</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>14.15362214907805</v>
+        <v>16.92013221904577</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.8381133387868664</v>
+        <v>0.8655224415612686</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0955417961910941</v>
+        <v>0.2709081914486235</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>8032</v>
+        <v>7705</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>143.2755252914885</v>
+        <v>163.6304006189191</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>36.2</v>
+        <v>29.7</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>54.41996566771548</v>
+        <v>39.91397839699843</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>16.51941168357176</v>
+        <v>11.51569553719792</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.613904323079008</v>
+        <v>0.4277513901819315</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.1926009235733216</v>
+        <v>0.0059072102867633</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6890</v>
+        <v>6931</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>131.0163193161552</v>
+        <v>144.3634159972653</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>148.5</v>
+        <v>38.9</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>38.87052522829402</v>
+        <v>37.80061069723362</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>10.3388236084375</v>
+        <v>14.15362212749436</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.6879684890715156</v>
+        <v>0.8381133387868664</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.4177504992368792</v>
+        <v>-0.09554179616884879</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6901</v>
+        <v>8032</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>123.6321671170766</v>
+        <v>143.2755252914885</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>16.65</v>
+        <v>36.2</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>58.10737279259873</v>
+        <v>54.41996527905984</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>18.37268684892686</v>
+        <v>16.51941168357176</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.902825851051072</v>
+        <v>0.613904323079008</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.2563378230827372</v>
+        <v>0.1926009238069936</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6996</v>
+        <v>6890</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>111.3494906471552</v>
+        <v>131.0163193161551</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>169.5</v>
+        <v>148.5</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,25 +6965,25 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>43.71801398879829</v>
+        <v>38.87052506832988</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>16.40529725585774</v>
+        <v>10.33882356942285</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.3019382895515251</v>
+        <v>0.6879684890715156</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M123" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.1221099687475746</v>
+        <v>0.4177504999045327</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6936</v>
+        <v>7803</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>96.25258172271027</v>
+        <v>112.2678274693798</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>32</v>
+        <v>17.8</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>47.63320060416208</v>
+        <v>35.7474966319042</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>19.15861837376199</v>
+        <v>12.02227750969982</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.1515984775026412</v>
+        <v>0.7291899769126228</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.0126381533890817</v>
+        <v>-0.0715349216107885</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>7803</v>
+        <v>6996</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>92.2678274693798</v>
+        <v>111.3494906471554</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>17.8</v>
+        <v>169.5</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>35.74749667462481</v>
+        <v>43.71801408174334</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>12.02227750153957</v>
+        <v>16.40529750214084</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.7291899769126228</v>
+        <v>0.3019382895515251</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0715349216107885</v>
+        <v>0.1221099681912405</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,52 +7099,105 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
+        <v>6936</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>永鴻生技</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>96.25258172271027</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>47.6332006394589</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>19.15861837527333</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.1515984775026412</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>-0.0126381534224583</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
         <v>7753</v>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>星亞</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D126" s="2" t="n">
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
         <v>78.42362799789579</v>
       </c>
-      <c r="E126" s="2" t="n">
+      <c r="E127" s="2" t="n">
         <v>35.7</v>
       </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>41.01826774116061</v>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>13.82623251649914</v>
-      </c>
-      <c r="J126" s="2" t="n">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>41.01826656329331</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>13.82623253262024</v>
+      </c>
+      <c r="J127" s="2" t="n">
         <v>1.160173034910806</v>
       </c>
-      <c r="K126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N126" s="2" t="n">
-        <v>0.0655938772616204</v>
-      </c>
-      <c r="O126" s="2" t="inlineStr">
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>0.0655938769500619</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
